--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕЛОР 20 ЕООД/ДЕЛОР 20 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕЛОР 20 ЕООД/ДЕЛОР 20 ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="69">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -73,6 +76,30 @@
     <t>2026-05-15</t>
   </si>
   <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
     <t>ДЛ1</t>
   </si>
   <si>
@@ -88,25 +115,94 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>18:11</t>
-  </si>
-  <si>
-    <t>10:48</t>
-  </si>
-  <si>
-    <t>15:47</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>12:22</t>
-  </si>
-  <si>
-    <t>19:37</t>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>13:55:00</t>
+  </si>
+  <si>
+    <t>18:11:00</t>
+  </si>
+  <si>
+    <t>10:47:00</t>
+  </si>
+  <si>
+    <t>15:47:00</t>
+  </si>
+  <si>
+    <t>12:05:00</t>
+  </si>
+  <si>
+    <t>12:22:00</t>
+  </si>
+  <si>
+    <t>19:37:00</t>
+  </si>
+  <si>
+    <t>15:52:00</t>
+  </si>
+  <si>
+    <t>06:57:00</t>
+  </si>
+  <si>
+    <t>23:27:00</t>
+  </si>
+  <si>
+    <t>06:50:00</t>
+  </si>
+  <si>
+    <t>10:37:00</t>
+  </si>
+  <si>
+    <t>20:37:00</t>
+  </si>
+  <si>
+    <t>07:12:00</t>
+  </si>
+  <si>
+    <t>3231298996 3231298996</t>
+  </si>
+  <si>
+    <t>3231382111 3231382111</t>
+  </si>
+  <si>
+    <t>3231649618 3231649618</t>
+  </si>
+  <si>
+    <t>3231650366 3231650366</t>
+  </si>
+  <si>
+    <t>3231735470 3231735470</t>
+  </si>
+  <si>
+    <t>3231790232 3231790232</t>
+  </si>
+  <si>
+    <t>3231937494 3231937494</t>
+  </si>
+  <si>
+    <t>3232066558 3232066558</t>
+  </si>
+  <si>
+    <t>3232099894 3232099894</t>
+  </si>
+  <si>
+    <t>3232162665 3232162665</t>
+  </si>
+  <si>
+    <t>3232195533 3232195533</t>
+  </si>
+  <si>
+    <t>3232472050 3232472050</t>
+  </si>
+  <si>
+    <t>3232587543 3232587543</t>
+  </si>
+  <si>
+    <t>3232633991 3232633991</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЕЛОР 20 ЕООД</t>
@@ -530,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -539,16 +635,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -588,365 +685,717 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1199</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>11.16</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2">
         <v>1.66</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>18.53</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.8</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>20.09</v>
       </c>
-      <c r="K2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>263532</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1199</v>
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F3">
         <v>11.11</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3">
         <v>1.66</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>18.44</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.8</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>20</v>
       </c>
-      <c r="K3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="M3">
-        <v>264002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4">
-        <v>1199</v>
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F4">
         <v>11.18</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4">
         <v>1.65</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>18.45</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.79</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>20.01</v>
       </c>
-      <c r="K4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4">
+      <c r="L4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="M4">
-        <v>265439</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5">
-        <v>1199</v>
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F5">
         <v>16.78</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5">
         <v>1.65</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>27.69</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.79</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>30.04</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
         <v>27</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>265531</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6">
-        <v>1199</v>
-      </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F6">
         <v>11.18</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6">
         <v>1.65</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>18.45</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.79</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>20.01</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>39</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
         <v>28</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>265895</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7">
-        <v>1199</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F7">
         <v>11.18</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7">
         <v>1.64</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>18.34</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.79</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>20.01</v>
       </c>
-      <c r="K7" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7">
+      <c r="L7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="M7">
-        <v>266183</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8">
-        <v>1199</v>
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F8">
         <v>14.2</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8">
         <v>1.63</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>23.15</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.76</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>24.99</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
         <v>30</v>
       </c>
-      <c r="L8">
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9">
+        <v>17.14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9">
+        <v>1.63</v>
+      </c>
+      <c r="I9" s="1">
+        <v>27.94</v>
+      </c>
+      <c r="J9">
+        <v>1.75</v>
+      </c>
+      <c r="K9" s="1">
+        <v>30</v>
+      </c>
+      <c r="L9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
-      <c r="M8">
-        <v>267201</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="4" t="s">
+      <c r="N9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10">
+        <v>1.48</v>
+      </c>
+      <c r="I10" s="1">
+        <v>14.8</v>
+      </c>
+      <c r="J10">
+        <v>1.55</v>
+      </c>
+      <c r="K10" s="1">
+        <v>15.5</v>
+      </c>
+      <c r="L10" t="s">
+        <v>43</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="F11">
+        <v>11.85</v>
+      </c>
+      <c r="G11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11">
+        <v>1.61</v>
+      </c>
+      <c r="I11" s="1">
+        <v>19.08</v>
+      </c>
+      <c r="J11">
+        <v>1.75</v>
+      </c>
+      <c r="K11" s="1">
+        <v>20.74</v>
+      </c>
+      <c r="L11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="F12">
+        <v>6.36</v>
+      </c>
+      <c r="G12" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="6">
-        <v>86.79000000000001</v>
-      </c>
-      <c r="C13" s="6">
-        <v>7</v>
-      </c>
-      <c r="D13" s="7">
-        <v>1.6482</v>
-      </c>
-      <c r="E13" s="6">
-        <v>143.05</v>
-      </c>
-      <c r="F13" s="6">
-        <v>155.15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="9">
-        <v>86.79000000000001</v>
-      </c>
-      <c r="C14" s="9">
-        <v>7</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="9">
-        <v>143.05</v>
-      </c>
-      <c r="F14" s="9">
-        <v>155.15</v>
+      <c r="H12">
+        <v>1.48</v>
+      </c>
+      <c r="I12" s="1">
+        <v>9.41</v>
+      </c>
+      <c r="J12">
+        <v>1.57</v>
+      </c>
+      <c r="K12" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="L12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13">
+        <v>14.54</v>
+      </c>
+      <c r="G13" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13">
+        <v>1.61</v>
+      </c>
+      <c r="I13" s="1">
+        <v>23.41</v>
+      </c>
+      <c r="J13">
+        <v>1.72</v>
+      </c>
+      <c r="K13" s="1">
+        <v>25.01</v>
+      </c>
+      <c r="L13" t="s">
+        <v>46</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="G14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14">
+        <v>1.6</v>
+      </c>
+      <c r="I14" s="1">
+        <v>14.19</v>
+      </c>
+      <c r="J14">
+        <v>1.7</v>
+      </c>
+      <c r="K14" s="1">
+        <v>15.08</v>
+      </c>
+      <c r="L14" t="s">
+        <v>47</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="G15" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15">
+        <v>1.5</v>
+      </c>
+      <c r="I15" s="1">
+        <v>14.57</v>
+      </c>
+      <c r="J15">
+        <v>1.57</v>
+      </c>
+      <c r="K15" s="1">
+        <v>15.24</v>
+      </c>
+      <c r="L15" t="s">
+        <v>48</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20" s="6">
+        <v>139.19</v>
+      </c>
+      <c r="C20" s="6">
+        <v>11</v>
+      </c>
+      <c r="D20" s="7">
+        <v>1.6357</v>
+      </c>
+      <c r="E20" s="6">
+        <v>227.67</v>
+      </c>
+      <c r="F20" s="6">
+        <v>245.98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="6">
+        <v>26.07</v>
+      </c>
+      <c r="C21" s="6">
+        <v>3</v>
+      </c>
+      <c r="D21" s="7">
+        <v>1.4875</v>
+      </c>
+      <c r="E21" s="6">
+        <v>38.78</v>
+      </c>
+      <c r="F21" s="6">
+        <v>40.73</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="9">
+        <v>165.26</v>
+      </c>
+      <c r="C22" s="9">
+        <v>14</v>
+      </c>
+      <c r="D22" s="7"/>
+      <c r="E22" s="9">
+        <v>266.45</v>
+      </c>
+      <c r="F22" s="9">
+        <v>286.71</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕЛОР 20 ЕООД/ДЕЛОР 20 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕЛОР 20 ЕООД/ДЕЛОР 20 ЕООД.xlsx
@@ -256,7 +256,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -266,12 +266,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -321,17 +315,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕЛОР 20 ЕООД/ДЕЛОР 20 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕЛОР 20 ЕООД/ДЕЛОР 20 ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="81">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-01</t>
   </si>
   <si>
@@ -82,10 +91,19 @@
     <t>2026-06-25</t>
   </si>
   <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>2026-06-28</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
   </si>
   <si>
     <t>ДЛ1</t>
@@ -100,70 +118,127 @@
     <t>78970151027720526</t>
   </si>
   <si>
+    <t>DIESEL EKONOMY</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>DIESEL EKONOMY</t>
-  </si>
-  <si>
-    <t>2026-06-01 07:17:41</t>
-  </si>
-  <si>
-    <t>2026-06-01 07:17:42</t>
-  </si>
-  <si>
-    <t>2026-06-02 08:08:58</t>
-  </si>
-  <si>
-    <t>2026-06-03 17:05:01</t>
-  </si>
-  <si>
-    <t>2026-06-08 06:40:51</t>
-  </si>
-  <si>
-    <t>2026-06-08 16:58:22</t>
-  </si>
-  <si>
-    <t>2026-06-11 12:26:43</t>
-  </si>
-  <si>
-    <t>2026-06-15 14:08:09</t>
-  </si>
-  <si>
-    <t>2026-06-15 17:14:26</t>
-  </si>
-  <si>
-    <t>2026-06-17 07:00:52</t>
-  </si>
-  <si>
-    <t>2026-06-17 07:00:53</t>
-  </si>
-  <si>
-    <t>2026-06-19 06:34:34</t>
-  </si>
-  <si>
-    <t>2026-06-19 08:38:27</t>
-  </si>
-  <si>
-    <t>2026-06-19 08:38:28</t>
-  </si>
-  <si>
-    <t>2026-06-23 07:55:59</t>
-  </si>
-  <si>
-    <t>2026-06-23 10:01:27</t>
-  </si>
-  <si>
-    <t>2026-06-23 14:00:28</t>
-  </si>
-  <si>
-    <t>2026-06-24 18:54:58</t>
-  </si>
-  <si>
-    <t>2026-06-25 05:47:21</t>
-  </si>
-  <si>
-    <t>2026-06-25 05:47:22</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>07:18:00</t>
+  </si>
+  <si>
+    <t>08:09:00</t>
+  </si>
+  <si>
+    <t>17:05:00</t>
+  </si>
+  <si>
+    <t>06:41:00</t>
+  </si>
+  <si>
+    <t>16:59:00</t>
+  </si>
+  <si>
+    <t>12:27:00</t>
+  </si>
+  <si>
+    <t>14:09:00</t>
+  </si>
+  <si>
+    <t>17:15:00</t>
+  </si>
+  <si>
+    <t>07:01:00</t>
+  </si>
+  <si>
+    <t>06:35:00</t>
+  </si>
+  <si>
+    <t>08:39:00</t>
+  </si>
+  <si>
+    <t>10:01:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>07:56:00</t>
+  </si>
+  <si>
+    <t>18:55:00</t>
+  </si>
+  <si>
+    <t>05:48:00</t>
+  </si>
+  <si>
+    <t>05:52:00</t>
+  </si>
+  <si>
+    <t>11:37:00</t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>3232719975 3232719975</t>
+  </si>
+  <si>
+    <t>3232768426 3232768426</t>
+  </si>
+  <si>
+    <t>3232816294 3232816294</t>
+  </si>
+  <si>
+    <t>3233056129 3233056129</t>
+  </si>
+  <si>
+    <t>3233063546 3233063546</t>
+  </si>
+  <si>
+    <t>3233207110 3233207110</t>
+  </si>
+  <si>
+    <t>3233399941 3233399941</t>
+  </si>
+  <si>
+    <t>3233404005 3233404005</t>
+  </si>
+  <si>
+    <t>3233487273 3233487273</t>
+  </si>
+  <si>
+    <t>3233590838 3233590838</t>
+  </si>
+  <si>
+    <t>3233592147 3233592147</t>
+  </si>
+  <si>
+    <t>3233748034 3233748034</t>
+  </si>
+  <si>
+    <t>3233748803 3233748803</t>
+  </si>
+  <si>
+    <t>3233770777 3233770777</t>
+  </si>
+  <si>
+    <t>3233825630 3233825630</t>
+  </si>
+  <si>
+    <t>3233864648 3233864648</t>
+  </si>
+  <si>
+    <t>3233941724 3233941724</t>
+  </si>
+  <si>
+    <t>3234019289 3234019289</t>
+  </si>
+  <si>
+    <t>3234066758 3234066758</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЕЛОР 20 ЕООД</t>
@@ -581,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -590,14 +665,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -631,798 +709,1163 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F2">
+        <v>29.6</v>
+      </c>
+      <c r="G2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2">
+        <v>1.59</v>
+      </c>
+      <c r="I2" s="1">
+        <v>47.06</v>
+      </c>
+      <c r="J2">
+        <v>1.69</v>
+      </c>
+      <c r="K2" s="1">
+        <v>50.02</v>
+      </c>
+      <c r="L2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3">
         <v>18.91</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3">
         <v>1.5</v>
       </c>
-      <c r="H2">
+      <c r="I3" s="1">
         <v>28.36</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J3">
         <v>1.57</v>
       </c>
-      <c r="J2">
+      <c r="K3" s="1">
         <v>29.69</v>
       </c>
-      <c r="K2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3">
-        <v>29.6</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.59</v>
-      </c>
-      <c r="H3">
-        <v>47.06</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="J3">
-        <v>50.02</v>
-      </c>
-      <c r="K3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F4">
         <v>19.01</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4">
         <v>1.5</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>28.52</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.57</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>29.85</v>
       </c>
-      <c r="K4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F5">
         <v>11.83</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5">
         <v>1.58</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>18.69</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.69</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>19.99</v>
       </c>
-      <c r="K5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F6">
         <v>19.28</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6">
         <v>1.48</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>28.53</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.56</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>30.08</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
       </c>
       <c r="F7">
         <v>12.2</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7">
         <v>1.55</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>18.91</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.64</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>20.01</v>
       </c>
-      <c r="K7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F8">
         <v>12.34</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8">
         <v>1.53</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>18.88</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.62</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>19.99</v>
       </c>
-      <c r="K8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F9">
         <v>12.5</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9">
         <v>1.53</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>19.12</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.6</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>20</v>
       </c>
-      <c r="K9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F10">
         <v>12.5</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10">
         <v>1.53</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>19.12</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.6</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>20</v>
       </c>
-      <c r="K10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F11">
         <v>12.58</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11">
         <v>1.52</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>19.12</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.59</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>20</v>
       </c>
-      <c r="K11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11" t="s">
+        <v>45</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F12">
         <v>5.82</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12">
         <v>1.44</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>8.380000000000001</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.55</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>9.02</v>
       </c>
-      <c r="K12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" t="s">
+        <v>45</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F13">
         <v>12.82</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13">
         <v>1.52</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>19.49</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>1.56</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>20</v>
       </c>
-      <c r="K13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13" t="s">
+        <v>46</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14">
+        <v>19.25</v>
+      </c>
+      <c r="G14" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14">
+        <v>1.52</v>
+      </c>
+      <c r="I14" s="1">
+        <v>29.26</v>
+      </c>
+      <c r="J14">
+        <v>1.56</v>
+      </c>
+      <c r="K14" s="1">
+        <v>30.03</v>
+      </c>
+      <c r="L14" t="s">
+        <v>47</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15">
+        <v>8.77</v>
+      </c>
+      <c r="G15" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15">
+        <v>1.44</v>
+      </c>
+      <c r="I15" s="1">
+        <v>12.63</v>
+      </c>
+      <c r="J15">
+        <v>1.54</v>
+      </c>
+      <c r="K15" s="1">
+        <v>13.51</v>
+      </c>
+      <c r="L15" t="s">
+        <v>47</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
         <v>22</v>
       </c>
-      <c r="C14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14">
-        <v>8.77</v>
-      </c>
-      <c r="G14" s="1">
-        <v>1.44</v>
-      </c>
-      <c r="H14">
-        <v>12.63</v>
-      </c>
-      <c r="I14" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="J14">
-        <v>13.51</v>
-      </c>
-      <c r="K14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="G16" t="s">
+        <v>36</v>
+      </c>
+      <c r="H16">
+        <v>1.41</v>
+      </c>
+      <c r="I16" s="1">
+        <v>11.69</v>
+      </c>
+      <c r="J16">
+        <v>1.51</v>
+      </c>
+      <c r="K16" s="1">
+        <v>12.52</v>
+      </c>
+      <c r="L16" t="s">
+        <v>48</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
         <v>22</v>
       </c>
-      <c r="C15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="B17" t="s">
         <v>29</v>
       </c>
-      <c r="F15">
-        <v>19.25</v>
-      </c>
-      <c r="G15" s="1">
+      <c r="C17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17">
+        <v>4.95</v>
+      </c>
+      <c r="G17" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17">
+        <v>1.41</v>
+      </c>
+      <c r="I17" s="1">
+        <v>6.98</v>
+      </c>
+      <c r="J17">
+        <v>1.51</v>
+      </c>
+      <c r="K17" s="1">
+        <v>7.47</v>
+      </c>
+      <c r="L17" t="s">
+        <v>49</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18">
+        <v>6.58</v>
+      </c>
+      <c r="G18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18">
+        <v>1.46</v>
+      </c>
+      <c r="I18" s="1">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="J18">
         <v>1.52</v>
       </c>
-      <c r="H15">
-        <v>29.26</v>
-      </c>
-      <c r="I15" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J15">
-        <v>30.03</v>
-      </c>
-      <c r="K15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16">
-        <v>6.58</v>
-      </c>
-      <c r="G16" s="1">
-        <v>1.46</v>
-      </c>
-      <c r="H16">
-        <v>9.609999999999999</v>
-      </c>
-      <c r="I16" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J16">
+      <c r="K18" s="1">
         <v>10</v>
       </c>
-      <c r="K16" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="L18" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
         <v>23</v>
       </c>
-      <c r="C17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="G17" s="1">
-        <v>1.41</v>
-      </c>
-      <c r="H17">
-        <v>11.69</v>
-      </c>
-      <c r="I17" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J17">
-        <v>12.52</v>
-      </c>
-      <c r="K17" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18">
-        <v>4.95</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1.41</v>
-      </c>
-      <c r="H18">
-        <v>6.98</v>
-      </c>
-      <c r="I18" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J18">
-        <v>7.47</v>
-      </c>
-      <c r="K18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F19">
         <v>13.27</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" t="s">
+        <v>36</v>
+      </c>
+      <c r="H19">
         <v>1.45</v>
       </c>
-      <c r="H19">
+      <c r="I19" s="1">
         <v>19.24</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19">
         <v>1.51</v>
       </c>
-      <c r="J19">
+      <c r="K19" s="1">
         <v>20.04</v>
       </c>
-      <c r="K19" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20">
+        <v>13.24</v>
+      </c>
+      <c r="G20" t="s">
+        <v>36</v>
+      </c>
+      <c r="H20">
+        <v>1.45</v>
+      </c>
+      <c r="I20" s="1">
+        <v>19.2</v>
+      </c>
+      <c r="J20">
+        <v>1.51</v>
+      </c>
+      <c r="K20" s="1">
+        <v>19.99</v>
+      </c>
+      <c r="L20" t="s">
+        <v>52</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
         <v>24</v>
       </c>
-      <c r="D20" t="s">
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21">
+        <v>10.63</v>
+      </c>
+      <c r="G21" t="s">
+        <v>36</v>
+      </c>
+      <c r="H21">
+        <v>1.4</v>
+      </c>
+      <c r="I21" s="1">
+        <v>14.88</v>
+      </c>
+      <c r="J21">
+        <v>1.51</v>
+      </c>
+      <c r="K21" s="1">
+        <v>16.05</v>
+      </c>
+      <c r="L21" t="s">
+        <v>52</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22">
+        <v>9.93</v>
+      </c>
+      <c r="G22" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22">
+        <v>1.43</v>
+      </c>
+      <c r="I22" s="1">
+        <v>14.2</v>
+      </c>
+      <c r="J22">
+        <v>1.51</v>
+      </c>
+      <c r="K22" s="1">
+        <v>14.99</v>
+      </c>
+      <c r="L22" t="s">
+        <v>53</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23">
+        <v>4.7</v>
+      </c>
+      <c r="G23" t="s">
+        <v>36</v>
+      </c>
+      <c r="H23">
+        <v>1.39</v>
+      </c>
+      <c r="I23" s="1">
+        <v>6.53</v>
+      </c>
+      <c r="J23">
+        <v>1.5</v>
+      </c>
+      <c r="K23" s="1">
+        <v>7.05</v>
+      </c>
+      <c r="L23" t="s">
+        <v>53</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
         <v>26</v>
       </c>
-      <c r="E20" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20">
-        <v>10.63</v>
-      </c>
-      <c r="G20" s="1">
-        <v>1.4</v>
-      </c>
-      <c r="H20">
-        <v>14.88</v>
-      </c>
-      <c r="I20" s="1">
+      <c r="B24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24">
+        <v>13.25</v>
+      </c>
+      <c r="G24" t="s">
+        <v>36</v>
+      </c>
+      <c r="H24">
+        <v>1.43</v>
+      </c>
+      <c r="I24" s="1">
+        <v>18.95</v>
+      </c>
+      <c r="J24">
         <v>1.51</v>
       </c>
-      <c r="J20">
-        <v>16.05</v>
-      </c>
-      <c r="K20" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="K24" s="1">
+        <v>20.01</v>
+      </c>
+      <c r="L24" t="s">
+        <v>54</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="G25" t="s">
+        <v>36</v>
+      </c>
+      <c r="H25">
+        <v>1.42</v>
+      </c>
+      <c r="I25" s="1">
+        <v>14.13</v>
+      </c>
+      <c r="J25">
+        <v>1.51</v>
+      </c>
+      <c r="K25" s="1">
+        <v>15.02</v>
+      </c>
+      <c r="L25" t="s">
+        <v>55</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="6">
+        <v>201.84</v>
+      </c>
+      <c r="C30" s="6">
+        <v>15</v>
+      </c>
+      <c r="D30" s="7">
+        <v>1.511</v>
+      </c>
+      <c r="E30" s="6">
+        <v>304.98</v>
+      </c>
+      <c r="F30" s="6">
+        <v>320.09</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="6">
+        <v>100.36</v>
+      </c>
+      <c r="C31" s="6">
+        <v>9</v>
+      </c>
+      <c r="D31" s="7">
+        <v>1.4597</v>
+      </c>
+      <c r="E31" s="6">
+        <v>146.5</v>
+      </c>
+      <c r="F31" s="6">
+        <v>155.24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" s="9">
+        <v>302.2</v>
+      </c>
+      <c r="C32" s="9">
         <v>24</v>
       </c>
-      <c r="D21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21">
-        <v>13.24</v>
-      </c>
-      <c r="G21" s="1">
-        <v>1.45</v>
-      </c>
-      <c r="H21">
-        <v>19.2</v>
-      </c>
-      <c r="I21" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J21">
-        <v>19.99</v>
-      </c>
-      <c r="K21" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="6">
-        <v>168.71</v>
-      </c>
-      <c r="C26" s="6">
-        <v>12</v>
-      </c>
-      <c r="D26" s="7">
-        <v>1.5275</v>
-      </c>
-      <c r="E26" s="6">
-        <v>257.7</v>
-      </c>
-      <c r="F26" s="6">
-        <v>270.07</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="6">
-        <v>95.66</v>
-      </c>
-      <c r="C27" s="6">
-        <v>8</v>
-      </c>
-      <c r="D27" s="7">
-        <v>1.4632</v>
-      </c>
-      <c r="E27" s="6">
-        <v>139.97</v>
-      </c>
-      <c r="F27" s="6">
-        <v>148.19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" s="9">
-        <v>264.37</v>
-      </c>
-      <c r="C28" s="9">
-        <v>20</v>
-      </c>
-      <c r="D28" s="7"/>
-      <c r="E28" s="9">
-        <v>397.67</v>
-      </c>
-      <c r="F28" s="9">
-        <v>418.26</v>
+      <c r="D32" s="7"/>
+      <c r="E32" s="9">
+        <v>451.48</v>
+      </c>
+      <c r="F32" s="9">
+        <v>475.33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A28:F28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕЛОР 20 ЕООД/ДЕЛОР 20 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕЛОР 20 ЕООД/ДЕЛОР 20 ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="74">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-01</t>
   </si>
   <si>
@@ -73,10 +79,28 @@
     <t>2026-07-13</t>
   </si>
   <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Варна Порт</t>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
   </si>
   <si>
     <t>ДЛ1</t>
@@ -97,40 +121,103 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-07-01 07:10:32</t>
-  </si>
-  <si>
-    <t>2026-07-01 21:41:00</t>
-  </si>
-  <si>
-    <t>2026-07-02 10:23:30</t>
-  </si>
-  <si>
-    <t>2026-07-02 20:21:44</t>
-  </si>
-  <si>
-    <t>2026-07-05 06:42:59</t>
-  </si>
-  <si>
-    <t>2026-07-05 06:43:00</t>
-  </si>
-  <si>
-    <t>2026-07-07 07:19:55</t>
-  </si>
-  <si>
-    <t>2026-07-07 09:45:42</t>
-  </si>
-  <si>
-    <t>2026-07-08 11:55:37</t>
-  </si>
-  <si>
-    <t>2026-07-09 06:06:42</t>
-  </si>
-  <si>
-    <t>2026-07-09 06:06:43</t>
-  </si>
-  <si>
-    <t>2026-07-13 09:46:00</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>21:41:00</t>
+  </si>
+  <si>
+    <t>07:11:00</t>
+  </si>
+  <si>
+    <t>10:23:00</t>
+  </si>
+  <si>
+    <t>20:22:00</t>
+  </si>
+  <si>
+    <t>06:43:00</t>
+  </si>
+  <si>
+    <t>07:20:00</t>
+  </si>
+  <si>
+    <t>09:45:00</t>
+  </si>
+  <si>
+    <t>11:56:00</t>
+  </si>
+  <si>
+    <t>06:07:00</t>
+  </si>
+  <si>
+    <t>09:46:00</t>
+  </si>
+  <si>
+    <t>20:04:00</t>
+  </si>
+  <si>
+    <t>10:26:00</t>
+  </si>
+  <si>
+    <t>14:33:00</t>
+  </si>
+  <si>
+    <t>07:28:00</t>
+  </si>
+  <si>
+    <t>12:50:00</t>
+  </si>
+  <si>
+    <t>17:31:00</t>
+  </si>
+  <si>
+    <t>3234151264 3234151264</t>
+  </si>
+  <si>
+    <t>3234161390 3234161390</t>
+  </si>
+  <si>
+    <t>3234199664 3234199664</t>
+  </si>
+  <si>
+    <t>3234216736 3234216736</t>
+  </si>
+  <si>
+    <t>3234355895 3234355895</t>
+  </si>
+  <si>
+    <t>3234448735 3234448735</t>
+  </si>
+  <si>
+    <t>3234434487 3234434487</t>
+  </si>
+  <si>
+    <t>3234485619 3234485619</t>
+  </si>
+  <si>
+    <t>3234545494 3234545494</t>
+  </si>
+  <si>
+    <t>3234747381 3234747381</t>
+  </si>
+  <si>
+    <t>3234899965 3234899965</t>
+  </si>
+  <si>
+    <t>3235352695 3235352695</t>
+  </si>
+  <si>
+    <t>3235533649 3235533649</t>
+  </si>
+  <si>
+    <t>3235539182 3235539182</t>
+  </si>
+  <si>
+    <t>3235543376 3235543376</t>
+  </si>
+  <si>
+    <t>3235659296 3235659296</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЕЛОР 20 ЕООД</t>
@@ -548,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -557,15 +644,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -602,554 +691,896 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2">
+        <v>6.64</v>
+      </c>
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2">
+        <v>1.42</v>
+      </c>
+      <c r="I2" s="1">
+        <v>9.43</v>
+      </c>
+      <c r="J2">
+        <v>1.51</v>
+      </c>
+      <c r="K2" s="1">
+        <v>10.03</v>
+      </c>
+      <c r="L2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>25</v>
       </c>
-      <c r="F2">
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3">
         <v>6.62</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3">
         <v>1.42</v>
       </c>
-      <c r="H2">
+      <c r="I3" s="1">
         <v>9.4</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J3">
         <v>1.51</v>
       </c>
-      <c r="J2">
+      <c r="K3" s="1">
         <v>10</v>
       </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3">
-        <v>6.64</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.42</v>
-      </c>
-      <c r="H3">
-        <v>9.43</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="J3">
-        <v>10.03</v>
-      </c>
-      <c r="K3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>19.87</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4">
         <v>1.42</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>28.22</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.51</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>30</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
         <v>29</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>6.74</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5">
         <v>1.42</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>9.57</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.51</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>10.18</v>
       </c>
-      <c r="K5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="L5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F6">
+        <v>17.84</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6">
+        <v>1.43</v>
+      </c>
+      <c r="I6" s="1">
+        <v>25.51</v>
+      </c>
+      <c r="J6">
+        <v>1.52</v>
+      </c>
+      <c r="K6" s="1">
+        <v>27.12</v>
+      </c>
+      <c r="L6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7">
         <v>3.33</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7">
         <v>1.38</v>
       </c>
-      <c r="H6">
+      <c r="I7" s="1">
         <v>4.6</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J7">
         <v>1.5</v>
       </c>
-      <c r="J6">
+      <c r="K7" s="1">
         <v>5</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
         <v>31</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7">
-        <v>17.84</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1.43</v>
-      </c>
-      <c r="H7">
-        <v>25.51</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J7">
-        <v>27.12</v>
-      </c>
-      <c r="K7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F8">
         <v>13.16</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8">
         <v>1.43</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>18.82</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.52</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>20</v>
       </c>
-      <c r="K8" t="s">
-        <v>33</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="L8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F9">
         <v>10.84</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9">
         <v>1.43</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>15.5</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.53</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>16.59</v>
       </c>
-      <c r="K9" t="s">
-        <v>34</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+      <c r="L9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F10">
         <v>19.74</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10">
         <v>1.43</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>28.23</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.52</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>30</v>
       </c>
-      <c r="K10" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+      <c r="L10" t="s">
+        <v>43</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11">
+        <v>16.45</v>
+      </c>
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11">
+        <v>1.43</v>
+      </c>
+      <c r="I11" s="1">
+        <v>23.52</v>
+      </c>
+      <c r="J11">
+        <v>1.52</v>
+      </c>
+      <c r="K11" s="1">
+        <v>25</v>
+      </c>
+      <c r="L11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="C11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11">
+      <c r="B12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12">
         <v>6.72</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12">
         <v>1.38</v>
       </c>
-      <c r="H11">
+      <c r="I12" s="1">
         <v>9.27</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J12">
         <v>1.49</v>
       </c>
-      <c r="J11">
+      <c r="K12" s="1">
         <v>10.01</v>
       </c>
-      <c r="K11" t="s">
-        <v>36</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="L12" t="s">
+        <v>44</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
         <v>25</v>
       </c>
-      <c r="F12">
-        <v>16.45</v>
-      </c>
-      <c r="G12" s="1">
-        <v>1.43</v>
-      </c>
-      <c r="H12">
-        <v>23.52</v>
-      </c>
-      <c r="I12" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="J12">
-        <v>25</v>
-      </c>
-      <c r="K12" t="s">
-        <v>37</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" t="s">
-        <v>19</v>
-      </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F13">
         <v>19.24</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13">
         <v>1.47</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>28.28</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>1.56</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>30.01</v>
       </c>
-      <c r="K13" t="s">
-        <v>38</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="5" t="s">
+      <c r="L13" t="s">
+        <v>45</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14">
+        <v>31.06</v>
+      </c>
+      <c r="G14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14">
+        <v>1.52</v>
+      </c>
+      <c r="I14" s="1">
+        <v>47.21</v>
+      </c>
+      <c r="J14">
+        <v>1.61</v>
+      </c>
+      <c r="K14" s="1">
+        <v>50.01</v>
+      </c>
+      <c r="L14" t="s">
+        <v>46</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="6">
-        <v>137.14</v>
-      </c>
-      <c r="C18" s="6">
+      <c r="C15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15">
+        <v>11.49</v>
+      </c>
+      <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15">
+        <v>1.64</v>
+      </c>
+      <c r="I15" s="1">
+        <v>18.84</v>
+      </c>
+      <c r="J15">
+        <v>1.74</v>
+      </c>
+      <c r="K15" s="1">
+        <v>19.99</v>
+      </c>
+      <c r="L15" t="s">
+        <v>47</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16">
+        <v>8.57</v>
+      </c>
+      <c r="G16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16">
+        <v>1.69</v>
+      </c>
+      <c r="I16" s="1">
+        <v>14.48</v>
+      </c>
+      <c r="J16">
+        <v>1.75</v>
+      </c>
+      <c r="K16" s="1">
+        <v>15</v>
+      </c>
+      <c r="L16" t="s">
+        <v>48</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17">
+        <v>8.58</v>
+      </c>
+      <c r="G17" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17">
+        <v>1.69</v>
+      </c>
+      <c r="I17" s="1">
+        <v>14.5</v>
+      </c>
+      <c r="J17">
+        <v>1.75</v>
+      </c>
+      <c r="K17" s="1">
+        <v>15.02</v>
+      </c>
+      <c r="L17" t="s">
+        <v>49</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18">
+        <v>5.71</v>
+      </c>
+      <c r="G18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18">
+        <v>1.69</v>
+      </c>
+      <c r="I18" s="1">
+        <v>9.65</v>
+      </c>
+      <c r="J18">
+        <v>1.75</v>
+      </c>
+      <c r="K18" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="L18" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="G19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19">
+        <v>1.71</v>
+      </c>
+      <c r="I19" s="1">
+        <v>14.48</v>
+      </c>
+      <c r="J19">
+        <v>1.77</v>
+      </c>
+      <c r="K19" s="1">
+        <v>14.99</v>
+      </c>
+      <c r="L19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="7">
-        <v>1.4327</v>
-      </c>
-      <c r="E18" s="6">
-        <v>196.48</v>
-      </c>
-      <c r="F18" s="6">
-        <v>208.93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="6">
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="6">
+        <v>211.02</v>
+      </c>
+      <c r="C24" s="6">
+        <v>16</v>
+      </c>
+      <c r="D24" s="7">
+        <v>1.4958</v>
+      </c>
+      <c r="E24" s="6">
+        <v>315.64</v>
+      </c>
+      <c r="F24" s="6">
+        <v>333.93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="6">
         <v>10.05</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C25" s="6">
         <v>2</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D25" s="7">
         <v>1.3801</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E25" s="6">
         <v>13.87</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F25" s="6">
         <v>15.01</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B20" s="9">
-        <v>147.19</v>
-      </c>
-      <c r="C20" s="9">
-        <v>12</v>
-      </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="9">
-        <v>210.35</v>
-      </c>
-      <c r="F20" s="9">
-        <v>223.94</v>
+    <row r="26" spans="1:14">
+      <c r="A26" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="9">
+        <v>221.07</v>
+      </c>
+      <c r="C26" s="9">
+        <v>18</v>
+      </c>
+      <c r="D26" s="7"/>
+      <c r="E26" s="9">
+        <v>329.51</v>
+      </c>
+      <c r="F26" s="9">
+        <v>348.94</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A22:F22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕЛОР 20 ЕООД/ДЕЛОР 20 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕЛОР 20 ЕООД/ДЕЛОР 20 ЕООД.xlsx
@@ -244,7 +244,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1531,7 +1531,7 @@
         <v>16</v>
       </c>
       <c r="D24" s="7">
-        <v>1.4958</v>
+        <v>1.495782</v>
       </c>
       <c r="E24" s="6">
         <v>315.64</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕЛОР 20 ЕООД/ДЕЛОР 20 ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЕЛОР 20 ЕООД/ДЕЛОР 20 ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="74">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -246,8 +243,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -340,10 +337,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -638,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -651,13 +648,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -700,859 +697,802 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2">
         <v>6.642</v>
       </c>
       <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2">
+        <v>1.419</v>
+      </c>
+      <c r="I2" s="1">
+        <v>9.425000000000001</v>
+      </c>
+      <c r="J2">
+        <v>1.51</v>
+      </c>
+      <c r="K2" s="1">
+        <v>10.029</v>
+      </c>
+      <c r="L2" t="s">
         <v>36</v>
       </c>
-      <c r="H2">
-        <v>1.399</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.419</v>
-      </c>
-      <c r="J2">
-        <v>9.424998</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L2" s="1">
-        <v>10.02942</v>
-      </c>
-      <c r="M2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>6.623</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H3">
-        <v>1.399</v>
+        <v>1.419</v>
       </c>
       <c r="I3" s="1">
-        <v>1.419</v>
+        <v>9.398</v>
       </c>
       <c r="J3">
-        <v>9.398037</v>
+        <v>1.51</v>
       </c>
       <c r="K3" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L3" s="1">
-        <v>10.00073</v>
-      </c>
-      <c r="M3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>10.001</v>
+      </c>
+      <c r="L3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4">
         <v>19.868</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H4">
-        <v>1.399</v>
+        <v>1.419</v>
       </c>
       <c r="I4" s="1">
-        <v>1.419</v>
+        <v>28.193</v>
       </c>
       <c r="J4">
-        <v>28.192692</v>
+        <v>1.51</v>
       </c>
       <c r="K4" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L4" s="1">
-        <v>30.00068</v>
-      </c>
-      <c r="M4" t="s">
-        <v>39</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>30.001</v>
+      </c>
+      <c r="L4" t="s">
+        <v>38</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>6.742</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5">
-        <v>1.399</v>
+        <v>1.419</v>
       </c>
       <c r="I5" s="1">
-        <v>1.419</v>
+        <v>9.567</v>
       </c>
       <c r="J5">
-        <v>9.566898</v>
+        <v>1.51</v>
       </c>
       <c r="K5" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L5" s="1">
-        <v>10.18042</v>
-      </c>
-      <c r="M5" t="s">
-        <v>40</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>10.18</v>
+      </c>
+      <c r="L5" t="s">
+        <v>39</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F6">
         <v>17.842</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H6">
-        <v>1.406</v>
+        <v>1.426</v>
       </c>
       <c r="I6" s="1">
-        <v>1.426</v>
+        <v>25.443</v>
       </c>
       <c r="J6">
-        <v>25.442692</v>
+        <v>1.52</v>
       </c>
       <c r="K6" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L6" s="1">
-        <v>27.11984</v>
-      </c>
-      <c r="M6" t="s">
-        <v>41</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>27.12</v>
+      </c>
+      <c r="L6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F7">
         <v>3.333</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H7">
-        <v>1.359</v>
+        <v>1.379</v>
       </c>
       <c r="I7" s="1">
-        <v>1.379</v>
+        <v>4.596</v>
       </c>
       <c r="J7">
-        <v>4.596207</v>
+        <v>1.5</v>
       </c>
       <c r="K7" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L7" s="1">
-        <v>4.9995</v>
-      </c>
-      <c r="M7" t="s">
-        <v>41</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+        <v>5</v>
+      </c>
+      <c r="L7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8">
         <v>13.158</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H8">
-        <v>1.406</v>
+        <v>1.426</v>
       </c>
       <c r="I8" s="1">
-        <v>1.426</v>
+        <v>18.763</v>
       </c>
       <c r="J8">
-        <v>18.763308</v>
+        <v>1.52</v>
       </c>
       <c r="K8" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L8" s="1">
-        <v>20.00016</v>
-      </c>
-      <c r="M8" t="s">
-        <v>42</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>20</v>
+      </c>
+      <c r="L8" t="s">
+        <v>41</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9">
         <v>10.843</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H9">
-        <v>1.406</v>
+        <v>1.426</v>
       </c>
       <c r="I9" s="1">
-        <v>1.426</v>
+        <v>15.462</v>
       </c>
       <c r="J9">
-        <v>15.462118</v>
+        <v>1.53</v>
       </c>
       <c r="K9" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L9" s="1">
-        <v>16.58979</v>
-      </c>
-      <c r="M9" t="s">
-        <v>43</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>16.59</v>
+      </c>
+      <c r="L9" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F10">
         <v>19.737</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H10">
-        <v>1.412</v>
+        <v>1.432</v>
       </c>
       <c r="I10" s="1">
-        <v>1.432</v>
+        <v>28.263</v>
       </c>
       <c r="J10">
-        <v>28.263384</v>
+        <v>1.52</v>
       </c>
       <c r="K10" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L10" s="1">
-        <v>30.00024</v>
-      </c>
-      <c r="M10" t="s">
-        <v>44</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>30</v>
+      </c>
+      <c r="L10" t="s">
+        <v>43</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F11">
         <v>16.447</v>
       </c>
       <c r="G11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H11">
-        <v>1.412</v>
+        <v>1.432</v>
       </c>
       <c r="I11" s="1">
-        <v>1.432</v>
+        <v>23.552</v>
       </c>
       <c r="J11">
-        <v>23.552104</v>
+        <v>1.52</v>
       </c>
       <c r="K11" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L11" s="1">
-        <v>24.99944</v>
-      </c>
-      <c r="M11" t="s">
-        <v>45</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>24.999</v>
+      </c>
+      <c r="L11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F12">
         <v>6.718</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H12">
-        <v>1.359</v>
+        <v>1.379</v>
       </c>
       <c r="I12" s="1">
-        <v>1.379</v>
+        <v>9.263999999999999</v>
       </c>
       <c r="J12">
-        <v>9.264122</v>
+        <v>1.49</v>
       </c>
       <c r="K12" s="1">
-        <v>1.49</v>
-      </c>
-      <c r="L12" s="1">
-        <v>10.00982</v>
-      </c>
-      <c r="M12" t="s">
-        <v>45</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>10.01</v>
+      </c>
+      <c r="L12" t="s">
+        <v>44</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F13">
         <v>19.237</v>
       </c>
       <c r="G13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H13">
-        <v>1.451</v>
+        <v>1.471</v>
       </c>
       <c r="I13" s="1">
-        <v>1.471</v>
+        <v>28.298</v>
       </c>
       <c r="J13">
-        <v>28.297627</v>
+        <v>1.56</v>
       </c>
       <c r="K13" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L13" s="1">
-        <v>30.00972</v>
-      </c>
-      <c r="M13" t="s">
-        <v>46</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>30.01</v>
+      </c>
+      <c r="L13" t="s">
+        <v>45</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F14">
         <v>31.056</v>
       </c>
       <c r="G14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H14">
-        <v>1.499</v>
+        <v>1.519</v>
       </c>
       <c r="I14" s="1">
-        <v>1.519</v>
+        <v>47.174</v>
       </c>
       <c r="J14">
-        <v>47.174064</v>
+        <v>1.61</v>
       </c>
       <c r="K14" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L14" s="1">
-        <v>50.00016</v>
-      </c>
-      <c r="M14" t="s">
-        <v>47</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>50</v>
+      </c>
+      <c r="L14" t="s">
+        <v>46</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F15">
         <v>11.489</v>
       </c>
       <c r="G15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H15">
-        <v>1.619</v>
+        <v>1.639</v>
       </c>
       <c r="I15" s="1">
-        <v>1.639</v>
+        <v>18.83</v>
       </c>
       <c r="J15">
-        <v>18.830471</v>
+        <v>1.74</v>
       </c>
       <c r="K15" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L15" s="1">
-        <v>19.99086</v>
-      </c>
-      <c r="M15" t="s">
-        <v>48</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>19.991</v>
+      </c>
+      <c r="L15" t="s">
+        <v>47</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F16">
         <v>8.571</v>
       </c>
       <c r="G16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H16">
-        <v>1.674</v>
+        <v>1.694</v>
       </c>
       <c r="I16" s="1">
-        <v>1.694</v>
+        <v>14.519</v>
       </c>
       <c r="J16">
-        <v>14.519274</v>
+        <v>1.75</v>
       </c>
       <c r="K16" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L16" s="1">
-        <v>14.99925</v>
-      </c>
-      <c r="M16" t="s">
-        <v>49</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>14.999</v>
+      </c>
+      <c r="L16" t="s">
+        <v>48</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F17">
         <v>8.583</v>
       </c>
       <c r="G17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H17">
-        <v>1.674</v>
+        <v>1.694</v>
       </c>
       <c r="I17" s="1">
-        <v>1.694</v>
+        <v>14.54</v>
       </c>
       <c r="J17">
-        <v>14.539602</v>
+        <v>1.75</v>
       </c>
       <c r="K17" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L17" s="1">
-        <v>15.02025</v>
-      </c>
-      <c r="M17" t="s">
-        <v>50</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+        <v>15.02</v>
+      </c>
+      <c r="L17" t="s">
+        <v>49</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F18">
         <v>5.709</v>
       </c>
       <c r="G18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H18">
-        <v>1.674</v>
+        <v>1.694</v>
       </c>
       <c r="I18" s="1">
-        <v>1.694</v>
+        <v>9.670999999999999</v>
       </c>
       <c r="J18">
-        <v>9.671046</v>
+        <v>1.75</v>
       </c>
       <c r="K18" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L18" s="1">
-        <v>9.99075</v>
-      </c>
-      <c r="M18" t="s">
-        <v>51</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+        <v>9.991</v>
+      </c>
+      <c r="L18" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" t="s">
         <v>25</v>
       </c>
-      <c r="B19" t="s">
-        <v>26</v>
-      </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F19">
         <v>8.468999999999999</v>
       </c>
       <c r="G19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H19">
-        <v>1.689</v>
+        <v>1.709</v>
       </c>
       <c r="I19" s="1">
-        <v>1.709</v>
+        <v>14.474</v>
       </c>
       <c r="J19">
-        <v>14.473521</v>
+        <v>1.77</v>
       </c>
       <c r="K19" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L19" s="1">
-        <v>14.99013</v>
-      </c>
-      <c r="M19" t="s">
-        <v>52</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
+        <v>14.99</v>
+      </c>
+      <c r="L19" t="s">
+        <v>51</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="3" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -1560,69 +1500,69 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:14">
       <c r="A23" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="C23" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>73</v>
-      </c>
       <c r="E23" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="6">
         <v>211.016</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="7">
         <v>16</v>
       </c>
       <c r="D24" s="7">
-        <v>1.495488</v>
-      </c>
-      <c r="E24" s="6">
-        <v>315.57</v>
-      </c>
-      <c r="F24" s="6">
-        <v>333.92</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+        <v>1.495</v>
+      </c>
+      <c r="E24" s="7">
+        <v>315.572</v>
+      </c>
+      <c r="F24" s="7">
+        <v>333.921</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" s="6">
         <v>10.051</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="7">
         <v>2</v>
       </c>
       <c r="D25" s="7">
         <v>1.379</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="7">
         <v>13.86</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="7">
         <v>15.01</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:14">
       <c r="A26" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B26" s="9">
         <v>221.067</v>
@@ -1632,10 +1572,10 @@
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="9">
-        <v>329.43</v>
+        <v>329.432</v>
       </c>
       <c r="F26" s="9">
-        <v>348.93</v>
+        <v>348.931</v>
       </c>
     </row>
   </sheetData>
